--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C15CC3-7A4C-0742-9E15-92C695DDE749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300A8C11-D955-844A-B3B7-A74284E37697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameSetting" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="159">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2663,6 +2663,80 @@
   </si>
   <si>
     <t>CottonCandyMinigame.SpaceBar</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxFamiliarSlotCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보유</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개수</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3187,7 +3261,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5" style="9"/>
@@ -3479,6 +3553,20 @@
       </c>
       <c r="D21" s="27" t="s">
         <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A22" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{300A8C11-D955-844A-B3B7-A74284E37697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6632B0-1844-9541-8B9A-B5010731ABC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameSetting" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="163">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2737,6 +2737,22 @@
       </rPr>
       <t>개수</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>사역마를 더 이상 소환할 수 없습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 사역마를 이미 지니고 있습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Familiar.DuplicationWarning</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Familiar.ExcessCountWarning</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3578,7 +3594,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F34DD51-2A97-5B40-A1F1-6327EBE79F11}">
-  <dimension ref="A1:XFA56"/>
+  <dimension ref="A1:XFA58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="44.83203125" customWidth="1"/>
@@ -8225,6 +8241,25 @@
         <v>155</v>
       </c>
     </row>
+    <row r="57" spans="1:5" ht="15">
+      <c r="A57" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="B57" s="30" t="s">
+        <v>159</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15">
+      <c r="A58" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="B58" s="30" t="s">
+        <v>160</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E6632B0-1844-9541-8B9A-B5010731ABC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDECF08B-59E5-3E43-886F-0DD5D7AD0866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8259,6 +8259,9 @@
       <c r="B58" s="30" t="s">
         <v>160</v>
       </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDECF08B-59E5-3E43-886F-0DD5D7AD0866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DA68B0-88ED-E242-8233-BCD036B0B468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="165">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2753,6 +2753,14 @@
   </si>
   <si>
     <t>Familiar.ExcessCountWarning</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryPopup.ItemCountZero</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템의 개수가 0개입니다.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3594,7 +3602,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F34DD51-2A97-5B40-A1F1-6327EBE79F11}">
-  <dimension ref="A1:XFA58"/>
+  <dimension ref="A1:XFA59"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="44.83203125" customWidth="1"/>
@@ -8263,6 +8271,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="59" spans="1:5" ht="15">
+      <c r="A59" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="B59" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DA68B0-88ED-E242-8233-BCD036B0B468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0117E5C-1C25-1147-903E-785C167B11B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameSetting" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="167">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2670,6 +2670,53 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t>사역마를 더 이상 소환할 수 없습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>해당 사역마를 이미 지니고 있습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Familiar.DuplicationWarning</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Familiar.ExcessCountWarning</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>InventoryPopup.ItemCountZero</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템의 개수가 0개입니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>StartFamiliarSlotCount</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기본</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
     <r>
       <rPr>
         <sz val="10"/>
@@ -2740,27 +2787,73 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>사역마를 더 이상 소환할 수 없습니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>해당 사역마를 이미 지니고 있습니다.</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Familiar.DuplicationWarning</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Familiar.ExcessCountWarning</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>InventoryPopup.ItemCountZero</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>아이템의 개수가 0개입니다.</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>최대 사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>해금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>가능</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>개수</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3285,7 +3378,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5" style="9"/>
@@ -3587,10 +3680,24 @@
         <v>157</v>
       </c>
       <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A23" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>164</v>
+      </c>
+      <c r="C23">
         <v>3</v>
       </c>
-      <c r="D22" s="27" t="s">
-        <v>158</v>
+      <c r="D23" s="27" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -8251,10 +8358,10 @@
     </row>
     <row r="57" spans="1:5" ht="15">
       <c r="A57" s="25" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B57" s="30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -8262,10 +8369,10 @@
     </row>
     <row r="58" spans="1:5" ht="15">
       <c r="A58" s="25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B58" s="30" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -8273,10 +8380,10 @@
     </row>
     <row r="59" spans="1:5" ht="15">
       <c r="A59" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="B59" s="30" t="s">
         <v>163</v>
-      </c>
-      <c r="B59" s="30" t="s">
-        <v>164</v>
       </c>
       <c r="E59">
         <v>1</v>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0117E5C-1C25-1147-903E-785C167B11B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC4B905-DA13-FD46-AA6D-AF9EB3D0D838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="173">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2854,6 +2854,96 @@
       </rPr>
       <t>개수</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarWorkingHours</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아르바이트</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}을/를 사용하여 {0}를 소환하시겠습니까?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Familiar.CallMessage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Familiar.SetWaitingState</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}을/를 바구니로 보낼까요?</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3378,7 +3468,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5" style="9"/>
@@ -3700,6 +3790,20 @@
         <v>165</v>
       </c>
     </row>
+    <row r="24" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A24" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24">
+        <v>4</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3709,7 +3813,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F34DD51-2A97-5B40-A1F1-6327EBE79F11}">
-  <dimension ref="A1:XFA59"/>
+  <dimension ref="A1:XFA61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="44.83203125" customWidth="1"/>
@@ -8389,6 +8493,28 @@
         <v>1</v>
       </c>
     </row>
+    <row r="60" spans="1:5" ht="15">
+      <c r="A60" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="B60" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="15">
+      <c r="A61" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="B61" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC4B905-DA13-FD46-AA6D-AF9EB3D0D838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468062CF-52DA-FA4A-8322-6B8B6BCDBF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameSetting" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="175">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2944,6 +2944,14 @@
   </si>
   <si>
     <t>{0}을/를 바구니로 보낼까요?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CancleButton</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>취소</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3813,7 +3821,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F34DD51-2A97-5B40-A1F1-6327EBE79F11}">
-  <dimension ref="A1:XFA61"/>
+  <dimension ref="A1:XFA62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="44.83203125" customWidth="1"/>
@@ -8307,29 +8315,29 @@
     </row>
     <row r="41" spans="1:5" ht="15">
       <c r="A41" s="25" t="s">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>112</v>
+        <v>174</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="15">
       <c r="A42" s="25" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B42" s="30" t="s">
-        <v>124</v>
-      </c>
-      <c r="E42">
-        <v>1</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="15">
       <c r="A43" s="25" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B43" s="30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E43">
         <v>1</v>
@@ -8337,10 +8345,10 @@
     </row>
     <row r="44" spans="1:5" ht="15">
       <c r="A44" s="25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B44" s="30" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E44">
         <v>1</v>
@@ -8348,53 +8356,53 @@
     </row>
     <row r="45" spans="1:5" ht="15">
       <c r="A45" s="25" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B45" s="30" t="s">
-        <v>113</v>
+        <v>126</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="15">
       <c r="A46" s="25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B46" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="15">
       <c r="A47" s="25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B47" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="15">
       <c r="A48" s="25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B48" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="15">
       <c r="A49" s="25" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B49" s="30" t="s">
-        <v>128</v>
-      </c>
-      <c r="E49">
-        <v>1</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="15">
       <c r="A50" s="25" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="B50" s="30" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -8402,29 +8410,29 @@
     </row>
     <row r="51" spans="1:5" ht="15">
       <c r="A51" s="25" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B51" s="30" t="s">
-        <v>146</v>
+        <v>144</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15">
       <c r="A52" s="25" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B52" s="30" t="s">
-        <v>150</v>
-      </c>
-      <c r="E52">
-        <v>1</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="15">
       <c r="A53" s="25" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B53" s="30" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E53">
         <v>1</v>
@@ -8432,10 +8440,10 @@
     </row>
     <row r="54" spans="1:5" ht="15">
       <c r="A54" s="25" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B54" s="30" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E54">
         <v>1</v>
@@ -8443,10 +8451,10 @@
     </row>
     <row r="55" spans="1:5" ht="15">
       <c r="A55" s="25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B55" s="30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E55">
         <v>1</v>
@@ -8454,29 +8462,29 @@
     </row>
     <row r="56" spans="1:5" ht="15">
       <c r="A56" s="25" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B56" s="30" t="s">
-        <v>155</v>
+        <v>154</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="15">
       <c r="A57" s="25" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B57" s="30" t="s">
-        <v>158</v>
-      </c>
-      <c r="E57">
-        <v>1</v>
+        <v>155</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15">
       <c r="A58" s="25" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B58" s="30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E58">
         <v>1</v>
@@ -8484,10 +8492,10 @@
     </row>
     <row r="59" spans="1:5" ht="15">
       <c r="A59" s="25" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B59" s="30" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -8495,10 +8503,10 @@
     </row>
     <row r="60" spans="1:5" ht="15">
       <c r="A60" s="25" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="B60" s="30" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -8506,12 +8514,23 @@
     </row>
     <row r="61" spans="1:5" ht="15">
       <c r="A61" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="B61" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="15">
+      <c r="A62" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="B61" s="30" t="s">
+      <c r="B62" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="E61">
+      <c r="E62">
         <v>1</v>
       </c>
     </row>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468062CF-52DA-FA4A-8322-6B8B6BCDBF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A69F4D-9247-7B49-9020-1ED226752058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2947,11 +2947,11 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>CancleButton</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>취소</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>CancelButton</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -8315,10 +8315,10 @@
     </row>
     <row r="41" spans="1:5" ht="15">
       <c r="A41" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="B41" s="30" t="s">
         <v>173</v>
-      </c>
-      <c r="B41" s="30" t="s">
-        <v>174</v>
       </c>
       <c r="E41">
         <v>1</v>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22A69F4D-9247-7B49-9020-1ED226752058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F307C7B-2B34-A346-BCC4-225B1EA5188F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2931,10 +2931,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>{0}을/를 사용하여 {0}를 소환하시겠습니까?</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>Familiar.CallMessage</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -2952,6 +2948,10 @@
   </si>
   <si>
     <t>CancelButton</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}을/를 사용하여 {1}를 소환하시겠습니까?</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -8315,10 +8315,10 @@
     </row>
     <row r="41" spans="1:5" ht="15">
       <c r="A41" s="25" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -8514,10 +8514,10 @@
     </row>
     <row r="61" spans="1:5" ht="15">
       <c r="A61" s="25" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -8525,10 +8525,10 @@
     </row>
     <row r="62" spans="1:5" ht="15">
       <c r="A62" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="B62" s="30" t="s">
         <v>171</v>
-      </c>
-      <c r="B62" s="30" t="s">
-        <v>172</v>
       </c>
       <c r="E62">
         <v>1</v>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F307C7B-2B34-A346-BCC4-225B1EA5188F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C630E163-EB75-8542-AB49-152368E22369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="177">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2935,10 +2935,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Familiar.SetWaitingState</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>{0}을/를 바구니로 보낼까요?</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -2952,6 +2948,18 @@
   </si>
   <si>
     <t>{0}을/를 사용하여 {1}를 소환하시겠습니까?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Familiar.SetIdleState</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Familiar.SetSummonedState</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>{0}와/과 동행하시겠습니까?</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3821,7 +3829,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F34DD51-2A97-5B40-A1F1-6327EBE79F11}">
-  <dimension ref="A1:XFA62"/>
+  <dimension ref="A1:XFA63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="44.83203125" customWidth="1"/>
@@ -8315,10 +8323,10 @@
     </row>
     <row r="41" spans="1:5" ht="15">
       <c r="A41" s="25" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B41" s="30" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E41">
         <v>1</v>
@@ -8517,7 +8525,7 @@
         <v>169</v>
       </c>
       <c r="B61" s="30" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -8525,12 +8533,23 @@
     </row>
     <row r="62" spans="1:5" ht="15">
       <c r="A62" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="B62" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="B62" s="30" t="s">
-        <v>171</v>
-      </c>
       <c r="E62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15">
+      <c r="A63" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="B63" s="30" t="s">
+        <v>176</v>
+      </c>
+      <c r="E63">
         <v>1</v>
       </c>
     </row>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C630E163-EB75-8542-AB49-152368E22369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110E8E9D-E6F0-7740-B6A4-A11C5B3CF5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameSetting" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="182">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -2960,6 +2960,157 @@
   </si>
   <si>
     <t>{0}와/과 동행하시겠습니까?</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마를</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소환하는데</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소요하는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> hp</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">int </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarSummonedConsumingHpPerHour</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarSummonedStartHp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소환</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> hp</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3484,7 +3635,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5" style="9"/>
@@ -3818,6 +3969,34 @@
       </c>
       <c r="D24" s="27" t="s">
         <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A25" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A26" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>179</v>
+      </c>
+      <c r="C26">
+        <v>10</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110E8E9D-E6F0-7740-B6A4-A11C5B3CF5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E414FE0-889B-AB4A-AC11-4E7E1C1404F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="181">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -3020,10 +3020,6 @@
       </rPr>
       <t xml:space="preserve"> hp</t>
     </r>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">int </t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -3976,7 +3972,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C25">
         <v>5</v>
@@ -3987,16 +3983,16 @@
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1">
       <c r="A26" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="26" t="s">
         <v>178</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>179</v>
       </c>
       <c r="C26">
         <v>10</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E414FE0-889B-AB4A-AC11-4E7E1C1404F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8334E43C-460E-C742-B1B3-D83B75583D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="183">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -3097,6 +3097,70 @@
         <charset val="129"/>
       </rPr>
       <t>소요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> hp</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarAutoRecoveryHpPerHour</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간당</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복</t>
     </r>
     <r>
       <rPr>
@@ -3631,7 +3695,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5" style="9"/>
@@ -3993,6 +4057,20 @@
       </c>
       <c r="D26" s="27" t="s">
         <v>180</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A27" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27">
+        <v>10</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8334E43C-460E-C742-B1B3-D83B75583D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF594FE4-C055-7F43-BE87-76B6DC13584B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="185">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -3170,6 +3170,156 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> hp</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarNoEnergyRecoveryHpHour</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>에너지가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>없어</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>잠들었을</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>때</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> hp 50% </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회복에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>걸리는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -3695,13 +3845,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5" style="9"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="46.1640625" customWidth="1"/>
-    <col min="4" max="4" width="45.33203125" customWidth="1"/>
+    <col min="4" max="4" width="49.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1">
@@ -4071,6 +4221,20 @@
       </c>
       <c r="D27" s="27" t="s">
         <v>182</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A28" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF594FE4-C055-7F43-BE87-76B6DC13584B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C89B288-7B01-354E-8B1C-2B971B21A0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4231,7 +4231,7 @@
         <v>183</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D28" s="27" t="s">
         <v>184</v>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C89B288-7B01-354E-8B1C-2B971B21A0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DBF4E1-ABA4-F647-9CB8-ED0ADD590B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameSetting" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="187">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -3321,6 +3321,14 @@
       </rPr>
       <t>시간</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Familiar.EmptySlotMessage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>소환할 사역마를 선택해주세요.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -4246,7 +4254,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F34DD51-2A97-5B40-A1F1-6327EBE79F11}">
-  <dimension ref="A1:XFA63"/>
+  <dimension ref="A1:XFA64"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="44.83203125" customWidth="1"/>
@@ -8970,6 +8978,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="64" spans="1:5" ht="15">
+      <c r="A64" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="B64" s="30" t="s">
+        <v>186</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DBF4E1-ABA4-F647-9CB8-ED0ADD590B1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AC9373-D64D-144A-8F2E-EC872C15018B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="189">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -3329,6 +3329,14 @@
   </si>
   <si>
     <t>소환할 사역마를 선택해주세요.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Familiar.EmptySlotNoFamiliarMessage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>소환할 수 있는 사역마가 없습니다.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -4254,7 +4262,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F34DD51-2A97-5B40-A1F1-6327EBE79F11}">
-  <dimension ref="A1:XFA64"/>
+  <dimension ref="A1:XFA65"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="44.83203125" customWidth="1"/>
@@ -8989,6 +8997,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="65" spans="1:5" ht="15">
+      <c r="A65" s="25" t="s">
+        <v>187</v>
+      </c>
+      <c r="B65" s="30" t="s">
+        <v>188</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8AC9373-D64D-144A-8F2E-EC872C15018B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E349CAB-92B5-D347-8088-64E2DBF6F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="191">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -3337,6 +3337,14 @@
   </si>
   <si>
     <t>소환할 수 있는 사역마가 없습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Familiar.LockedSlotMessage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>소환 바구니 개수를 늘릴 수 있는 아이템이 없습니다.</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -4262,7 +4270,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F34DD51-2A97-5B40-A1F1-6327EBE79F11}">
-  <dimension ref="A1:XFA65"/>
+  <dimension ref="A1:XFA66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="44.83203125" customWidth="1"/>
@@ -9008,6 +9016,17 @@
         <v>1</v>
       </c>
     </row>
+    <row r="66" spans="1:5" ht="15">
+      <c r="A66" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" s="30" t="s">
+        <v>190</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E349CAB-92B5-D347-8088-64E2DBF6F28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3B2525-68A5-C141-BA21-0B855DA7DA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="195">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -3345,6 +3345,118 @@
   </si>
   <si>
     <t>소환 바구니 개수를 늘릴 수 있는 아이템이 없습니다.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>사역마를 선택해주세요.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarSelectPopup.WorkingTimeMessage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarSelectPopup.NotSelectMessage</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>지금</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>보내면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> {0} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후에</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>복귀해요</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -3356,7 +3468,7 @@
     <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="[$₩-412]#,##0.00"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3491,6 +3603,13 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="나눔명조"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Malgun Gothic"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -4270,7 +4389,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F34DD51-2A97-5B40-A1F1-6327EBE79F11}">
-  <dimension ref="A1:XFA66"/>
+  <dimension ref="A1:XFA68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="44.83203125" customWidth="1"/>
@@ -9027,6 +9146,28 @@
         <v>1</v>
       </c>
     </row>
+    <row r="67" spans="1:5" ht="15">
+      <c r="A67" s="25" t="s">
+        <v>193</v>
+      </c>
+      <c r="B67" s="30" t="s">
+        <v>191</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="15">
+      <c r="A68" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="B68" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A3B2525-68A5-C141-BA21-0B855DA7DA8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F237B28E-F514-784C-BC70-2856984D73E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameSetting" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="197">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -3375,6 +3375,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3394,6 +3395,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> {0} </t>
@@ -3432,6 +3434,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -3456,6 +3459,70 @@
         <scheme val="minor"/>
       </rPr>
       <t>.</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarWorkingConsumingHp</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>사역마가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아르바이트하면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Malgun Gothic"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>소요되는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> hp</t>
     </r>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -3988,7 +4055,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5" style="9"/>
@@ -4378,6 +4445,20 @@
       </c>
       <c r="D28" s="27" t="s">
         <v>184</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="15.75" customHeight="1">
+      <c r="A29" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="C29">
+        <v>40</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F237B28E-F514-784C-BC70-2856984D73E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C152B5-C10A-C348-9D37-ACC7DBE5C385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GameSetting" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="199">
   <si>
     <t>Value</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -3524,6 +3524,14 @@
       </rPr>
       <t xml:space="preserve"> hp</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>DayFormat</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>D+{0}</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -4470,7 +4478,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F34DD51-2A97-5B40-A1F1-6327EBE79F11}">
-  <dimension ref="A1:XFA68"/>
+  <dimension ref="A1:XFA69"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="44.83203125" customWidth="1"/>
@@ -9249,6 +9257,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="69" spans="1:5" ht="15">
+      <c r="A69" s="25" t="s">
+        <v>197</v>
+      </c>
+      <c r="B69" s="30" t="s">
+        <v>198</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel/GameData.xlsx
+++ b/excel/GameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C152B5-C10A-C348-9D37-ACC7DBE5C385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FB80EE7-12FE-5244-A26A-ED7C922E89FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="680" windowWidth="28140" windowHeight="15100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9264,6 +9264,9 @@
       <c r="B69" s="30" t="s">
         <v>198</v>
       </c>
+      <c r="E69">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
